--- a/artfynd/A 8346-2024 artfynd.xlsx
+++ b/artfynd/A 8346-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133931863</v>
       </c>
       <c r="B2" t="n">
-        <v>57779</v>
+        <v>57786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133931885</v>
       </c>
       <c r="B3" t="n">
-        <v>57263</v>
+        <v>57270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133931852</v>
       </c>
       <c r="B4" t="n">
-        <v>58044</v>
+        <v>58051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>133931873</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8346-2024 artfynd.xlsx
+++ b/artfynd/A 8346-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133931863</v>
       </c>
       <c r="B2" t="n">
-        <v>57786</v>
+        <v>57796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133931885</v>
       </c>
       <c r="B3" t="n">
-        <v>57270</v>
+        <v>57280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133931852</v>
       </c>
       <c r="B4" t="n">
-        <v>58051</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>133931873</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8346-2024 artfynd.xlsx
+++ b/artfynd/A 8346-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133931863</v>
+        <v>133550689</v>
       </c>
       <c r="B2" t="n">
-        <v>57796</v>
+        <v>57269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102976</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karlslund, Nrk</t>
+          <t>Skrattorp, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515474</v>
+        <v>515327</v>
       </c>
       <c r="R2" t="n">
-        <v>6539806</v>
+        <v>6539761</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,12 +782,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133931852</v>
+        <v>133931873</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,37 +924,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -999,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1005,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mot norr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133931873</v>
+        <v>133931852</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>58061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,33 +1048,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100082</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1118,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,12 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mot norr</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,6 +1157,1175 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133931863</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57796</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Karlslund, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>515474</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539806</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133550639</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58519</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skrattorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>515327</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6539761</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133550705</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skrattorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>515327</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6539761</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133550772</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221154</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsstjärna</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lysimachia europaea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skrattorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>515327</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6539761</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133550760</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skrattorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>515327</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6539761</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133550809</v>
+      </c>
+      <c r="B11" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skrattorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>515327</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6539761</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133550944</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skrattorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>515327</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6539761</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133551051</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skrattorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>515327</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6539761</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133550917</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skrattorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>515327</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6539761</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133550869</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102871</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skrattorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>515327</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6539761</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helena Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8346-2024 artfynd.xlsx
+++ b/artfynd/A 8346-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931885</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931873</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931852</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1276,6 +1301,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133931863</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1395,6 +1425,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550639</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1514,6 +1549,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550705</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1630,6 +1670,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550772</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1746,6 +1791,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550760</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1862,6 +1912,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550809</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1978,6 +2033,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550944</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2094,6 +2154,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133551051</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2210,6 +2275,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550917</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2326,8 +2396,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133550869</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>